--- a/rpt/Journal de travail/carte_electronique_didactique_PittetL02-rpt-journal.xlsx
+++ b/rpt/Journal de travail/carte_electronique_didactique_PittetL02-rpt-journal.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eduetatfr-my.sharepoint.com/personal/loic_pittet_studentfr_ch/Documents/TPI_PITTETL02/tpi_carte_electronique_didactique_pittetl02/rpt/Journal de travail/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1000" documentId="11_416AEE08F1E9306E2D9B4F0BC9E4841233F83705" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0662815E-7331-47E8-8811-497838C45343}"/>
+  <xr:revisionPtr revIDLastSave="1064" documentId="11_416AEE08F1E9306E2D9B4F0BC9E4841233F83705" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{216B380F-14C9-443A-B12B-AEC934DE345A}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="15" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="154">
   <si>
     <t>Date</t>
   </si>
@@ -1295,7 +1295,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="fr-FR"/>
+          <a:endParaRPr lang="fr-CH"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -1504,6 +1504,27 @@
             </c:extLst>
           </c:dPt>
           <c:dLbls>
+            <c:dLbl>
+              <c:idx val="7"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="8.7366051955143787E-3"/>
+                  <c:y val="7.5553311255685776E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="1"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000F-9435-4535-B240-6A0044029AA7}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
             <c:spPr>
               <a:noFill/>
               <a:ln>
@@ -1530,7 +1551,6 @@
                 <a:endParaRPr lang="fr-FR"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="inEnd"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -1628,7 +1648,6 @@
           </c:extLst>
         </c:ser>
         <c:dLbls>
-          <c:dLblPos val="inEnd"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
           <c:showCatName val="0"/>
@@ -1733,7 +1752,818 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="fr-FR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="fr-CH"/>
+              <a:t>Graphique des heures prévu</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:pieChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="317500" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="25000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000004-FC5C-4852-A93F-E1D851FD484D}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="317500" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="25000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-FC5C-4852-A93F-E1D851FD484D}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="317500" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="25000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000006-FC5C-4852-A93F-E1D851FD484D}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="317500" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="25000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-FC5C-4852-A93F-E1D851FD484D}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="317500" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="25000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000008-FC5C-4852-A93F-E1D851FD484D}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="5"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="317500" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="25000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000002-FC5C-4852-A93F-E1D851FD484D}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="6"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="317500" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="25000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-FC5C-4852-A93F-E1D851FD484D}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="7"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="317500" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="25000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-FC5C-4852-A93F-E1D851FD484D}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:r>
+                      <a:rPr lang="en-US" baseline="0"/>
+                      <a:t> </a:t>
+                    </a:r>
+                    <a:fld id="{1A5E8BC6-929C-45BD-9A95-E4572A61E630}" type="PERCENTAGE">
+                      <a:rPr lang="en-US" baseline="0"/>
+                      <a:pPr/>
+                      <a:t>[POURCENTAGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US" baseline="0"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="inEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="1"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:showDataLabelsRange val="0"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000004-FC5C-4852-A93F-E1D851FD484D}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{FBDD90A3-7F4E-4EAC-8218-237C6E03FDC4}" type="PERCENTAGE">
+                      <a:rPr lang="en-US" baseline="0"/>
+                      <a:pPr/>
+                      <a:t>[POURCENTAGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="fr-CH"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="inEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="1"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:showDataLabelsRange val="0"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000005-FC5C-4852-A93F-E1D851FD484D}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{B215D4A7-5135-4168-9CEC-35526489D26B}" type="PERCENTAGE">
+                      <a:rPr lang="en-US" baseline="0"/>
+                      <a:pPr/>
+                      <a:t>[POURCENTAGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="fr-CH"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="inEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="1"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:showDataLabelsRange val="0"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000006-FC5C-4852-A93F-E1D851FD484D}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="3"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{5C6F8DE3-AFD7-471C-865E-A3AB3BFBAA8E}" type="PERCENTAGE">
+                      <a:rPr lang="en-US" baseline="0"/>
+                      <a:pPr/>
+                      <a:t>[POURCENTAGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="fr-CH"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="inEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="1"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:showDataLabelsRange val="0"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000007-FC5C-4852-A93F-E1D851FD484D}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="4"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{46151A90-52FB-4636-9B81-B86D473888F0}" type="PERCENTAGE">
+                      <a:rPr lang="en-US" baseline="0"/>
+                      <a:pPr/>
+                      <a:t>[POURCENTAGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="fr-CH"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="inEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="1"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:showDataLabelsRange val="0"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000008-FC5C-4852-A93F-E1D851FD484D}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="5"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:r>
+                      <a:rPr lang="en-US" baseline="0"/>
+                      <a:t> </a:t>
+                    </a:r>
+                    <a:fld id="{05318B57-499F-4444-9D3F-78BF83EEE8C9}" type="PERCENTAGE">
+                      <a:rPr lang="en-US" baseline="0"/>
+                      <a:pPr/>
+                      <a:t>[POURCENTAGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US" baseline="0"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="inEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="1"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:showDataLabelsRange val="0"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000002-FC5C-4852-A93F-E1D851FD484D}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="6"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{DF1E1856-5B12-4D18-9A29-2F2A12170496}" type="PERCENTAGE">
+                      <a:rPr lang="en-US" baseline="0"/>
+                      <a:pPr/>
+                      <a:t>[POURCENTAGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="fr-CH"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="inEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="1"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:showDataLabelsRange val="0"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000003-FC5C-4852-A93F-E1D851FD484D}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="7"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{880495CA-4DBD-4170-81F4-B86D7218C77E}" type="PERCENTAGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[POURCENTAGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="fr-CH"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="bestFit"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:showDataLabelsRange val="0"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000001-FC5C-4852-A93F-E1D851FD484D}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="fr-FR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="inEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="1"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="35000"/>
+                      <a:lumOff val="65000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:round/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>total!$B$20:$B$27</c:f>
+              <c:strCache>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>Discussion</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>PCB</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Programmation</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Production</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Tests</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Documentation</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Schematic</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Recherches</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>total!$C$20:$C$27</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-FC5C-4852-A93F-E1D851FD484D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="inEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:alpha val="78000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:pattFill prst="dkDnDiag">
+      <a:fgClr>
+        <a:schemeClr val="lt1">
+          <a:lumMod val="95000"/>
+        </a:schemeClr>
+      </a:fgClr>
+      <a:bgClr>
+        <a:schemeClr val="lt1"/>
+      </a:bgClr>
+    </a:pattFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="fr-FR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -2304,20 +3134,551 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="261">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="dkDnDiag">
+        <a:fgClr>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="lt1"/>
+        </a:bgClr>
+      </a:pattFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1">
+          <a:alpha val="75000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="317500" algn="ctr" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="25000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="88900" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="20000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+      <a:scene3d>
+        <a:camera prst="orthographicFront"/>
+        <a:lightRig rig="threePt" dir="t"/>
+      </a:scene3d>
+      <a:sp3d prstMaterial="matte"/>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1">
+          <a:alpha val="78000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1800" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>589084</xdr:colOff>
+      <xdr:colOff>605649</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>131518</xdr:rowOff>
+      <xdr:rowOff>164648</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>589084</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>17218</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>23812</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>23811</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2337,6 +3698,42 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>660538</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>178283</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>660538</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>63983</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Graphique 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{206B9F91-C893-9841-CCE6-7665740DE3CC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2621,7 +4018,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="B4:C12"/>
+  <dimension ref="B4:C28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
@@ -2693,6 +4090,78 @@
         <v>41</v>
       </c>
       <c r="C12">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>102</v>
+      </c>
+      <c r="C21">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C24">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C26">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B27" t="s">
+        <v>153</v>
+      </c>
+      <c r="C27">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
+        <v>41</v>
+      </c>
+      <c r="C28">
         <v>118</v>
       </c>
     </row>
@@ -2780,7 +4249,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:7" s="10" customFormat="1" ht="45" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" s="10" customFormat="1" ht="56.25" x14ac:dyDescent="0.2">
       <c r="A5" s="42" t="s">
         <v>6</v>
       </c>
@@ -2894,7 +4363,7 @@
       </c>
       <c r="G11" s="14"/>
     </row>
-    <row r="12" spans="1:7" s="10" customFormat="1" ht="157.5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" s="10" customFormat="1" ht="168.75" x14ac:dyDescent="0.2">
       <c r="A12" s="43" t="s">
         <v>5</v>
       </c>
@@ -2915,7 +4384,7 @@
       </c>
       <c r="G12" s="14"/>
     </row>
-    <row r="13" spans="1:7" s="10" customFormat="1" ht="146.25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" s="10" customFormat="1" ht="157.5" x14ac:dyDescent="0.2">
       <c r="A13" s="43"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4" t="s">
@@ -3100,7 +4569,7 @@
       </c>
       <c r="G23" s="14"/>
     </row>
-    <row r="24" spans="1:7" s="10" customFormat="1" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7" s="10" customFormat="1" ht="45" x14ac:dyDescent="0.2">
       <c r="A24" s="43"/>
       <c r="B24" s="4"/>
       <c r="C24" s="4" t="s">
@@ -4550,11 +6019,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
     <mergeCell ref="A29:A35"/>
     <mergeCell ref="A37:D37"/>
     <mergeCell ref="A38:G38"/>
@@ -4563,6 +6027,11 @@
     <mergeCell ref="A12:A15"/>
     <mergeCell ref="A17:A20"/>
     <mergeCell ref="A22:A27"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
   </mergeCells>
   <conditionalFormatting sqref="F5 F7:F11 F13:F21 F23:F26 F28:F30 F32 F36">
     <cfRule type="containsText" dxfId="23" priority="1" operator="containsText" text="Terminé">
@@ -5058,7 +6527,7 @@
     <mergeCell ref="A22:A27"/>
     <mergeCell ref="A29:A35"/>
   </mergeCells>
-  <conditionalFormatting sqref="F5 F23:F26 F28:F30 F32 F36 F7:F21">
+  <conditionalFormatting sqref="F5 F7:F21 F23:F26 F28:F30 F32 F36">
     <cfRule type="containsText" dxfId="19" priority="1" operator="containsText" text="Terminé">
       <formula>NOT(ISERROR(SEARCH("Terminé",F5)))</formula>
     </cfRule>
@@ -5519,6 +6988,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A33:G39"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="A27:A30"/>
+    <mergeCell ref="A32:D32"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A5:A10"/>
     <mergeCell ref="A12:A15"/>
@@ -5526,12 +7001,6 @@
     <mergeCell ref="A22:A25"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:B4"/>
-    <mergeCell ref="A33:G39"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="A27:A30"/>
-    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <conditionalFormatting sqref="F5:F31">
     <cfRule type="containsText" dxfId="15" priority="1" operator="containsText" text="Terminé">
@@ -6469,12 +7938,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
     <mergeCell ref="A33:G39"/>
     <mergeCell ref="A5:A10"/>
     <mergeCell ref="A12:A15"/>
@@ -6482,6 +7945,12 @@
     <mergeCell ref="A22:A25"/>
     <mergeCell ref="A27:A30"/>
     <mergeCell ref="A32:D32"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
   </mergeCells>
   <conditionalFormatting sqref="F5:F31">
     <cfRule type="containsText" dxfId="7" priority="1" operator="containsText" text="Terminé">
@@ -6940,12 +8409,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
     <mergeCell ref="A33:G39"/>
     <mergeCell ref="A5:A10"/>
     <mergeCell ref="A12:A15"/>
@@ -6953,6 +8416,12 @@
     <mergeCell ref="A22:A25"/>
     <mergeCell ref="A27:A30"/>
     <mergeCell ref="A32:D32"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
   </mergeCells>
   <conditionalFormatting sqref="F5:F31">
     <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="Terminé">
